--- a/akrami_Ex3A_tables.xlsx
+++ b/akrami_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayaeedarashullahakr\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AC2E77A7-7B18-49B9-B0EC-36FBB2B7229F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC699A50-A1E8-4264-A80E-97F69CE92929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3552" yWindow="3552" windowWidth="17280" windowHeight="9960" xr2:uid="{1108299C-4170-418C-818F-0CB701B95CEF}"/>
+    <workbookView xWindow="3552" yWindow="3552" windowWidth="17280" windowHeight="9960" activeTab="3" xr2:uid="{1108299C-4170-418C-818F-0CB701B95CEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Client" sheetId="1" r:id="rId1"/>
@@ -483,6 +483,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7F7863-A2E7-4DAB-A544-32D03808F584}">
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -510,6 +513,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C881A1-733B-4B6F-B817-BCF4887B3D15}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -540,6 +546,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6AB5C2A-141D-48A0-83A3-26AE329DF0A0}">
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -567,6 +578,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3F44A3-F509-4D49-8BBB-828996E6CF2A}">
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">

--- a/akrami_Ex3A_tables.xlsx
+++ b/akrami_Ex3A_tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayaeedarashullahakr\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC699A50-A1E8-4264-A80E-97F69CE92929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADDE020-A657-4075-A651-13D8B4A96634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3552" yWindow="3552" windowWidth="17280" windowHeight="9960" activeTab="3" xr2:uid="{1108299C-4170-418C-818F-0CB701B95CEF}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Client" sheetId="1" r:id="rId1"/>
     <sheet name="Dog" sheetId="2" r:id="rId2"/>
     <sheet name="Staff" sheetId="3" r:id="rId3"/>
-    <sheet name="Appointment" sheetId="4" r:id="rId4"/>
+    <sheet name="Appointments" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
